--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_224_R23.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_224_R23.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4014</v>
+        <v>6.4699</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4935</v>
+        <v>7.9653</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0922</v>
+        <v>-1.4955</v>
       </c>
       <c r="G2" t="n">
         <v>3.9471</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9181</v>
+        <v>0.9867</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6607</v>
+        <v>1.1325</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2574</v>
+        <v>-0.1458</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0443</v>
+        <v>4.2256</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1627</v>
+        <v>3.7472</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8817</v>
+        <v>0.4784</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2924</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>3.517</v>
+        <v>1.6983</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9451</v>
+        <v>1.5296</v>
       </c>
       <c r="U3" t="n">
-        <v>0.572</v>
+        <v>0.1687</v>
       </c>
       <c r="V3" t="n">
         <v>1.8919</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5495</v>
+        <v>1.623</v>
       </c>
       <c r="E4" t="n">
-        <v>4.079</v>
+        <v>3.2533</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5295</v>
+        <v>-1.6303</v>
       </c>
       <c r="G4" t="n">
         <v>1.2972</v>
@@ -766,13 +766,13 @@
         <v>0.232</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5564</v>
+        <v>0.63</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3486</v>
+        <v>0.523</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2078</v>
+        <v>0.107</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5361</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>F. NTILIKINA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3298</v>
+        <v>1.2084</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8373</v>
+        <v>-0.6788</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5075</v>
+        <v>1.8871</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1391</v>
+        <v>-0.6187</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3301</v>
+        <v>0.2413</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1911</v>
+        <v>-0.86</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3004</v>
+        <v>-1.2764</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2268</v>
+        <v>-0.3662</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0736</v>
+        <v>-0.9102</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1613</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1034</v>
+        <v>0.6075</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2647</v>
+        <v>0.0502</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9045</v>
+        <v>0.6673</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5702</v>
+        <v>0.5977</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3343</v>
+        <v>0.0696</v>
       </c>
       <c r="V5" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6563</v>
+        <v>1.0945</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5252</v>
+        <v>1.8373</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1311</v>
+        <v>-0.7427</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7226</v>
+        <v>0.1391</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0434</v>
+        <v>1.3301</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6792</v>
+        <v>-1.1911</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4031</v>
+        <v>1.3004</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2927</v>
+        <v>1.2268</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1104</v>
+        <v>0.0736</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1257</v>
+        <v>-1.1613</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3361</v>
+        <v>0.1034</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7896</v>
+        <v>-1.2647</v>
       </c>
       <c r="P6" t="n">
         <v>-0.9278</v>
@@ -922,28 +922,28 @@
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>2.3068</v>
+        <v>0.6693</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4416</v>
+        <v>0.5702</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1349</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. NTILIKINA</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5178</v>
+        <v>0.9469</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2685</v>
+        <v>2.416</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7863</v>
+        <v>-1.4691</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6187</v>
+        <v>2.5364</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2413</v>
+        <v>3.3394</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.86</v>
+        <v>-0.8031</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2764</v>
+        <v>5.3093</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3662</v>
+        <v>3.5829</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9102</v>
+        <v>1.7263</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6578000000000001</v>
+        <v>-2.7729</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6075</v>
+        <v>-0.2435</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0502</v>
+        <v>-2.5294</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0233</v>
+        <v>1.1037</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007900000000000001</v>
+        <v>1.7458</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0312</v>
+        <v>-0.642</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. MCKISSIC</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1144</v>
+        <v>0.338</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0536</v>
+        <v>3.8152</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.168</v>
+        <v>-3.4772</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0428</v>
+        <v>1.3773</v>
       </c>
       <c r="H8" t="n">
-        <v>0.006</v>
+        <v>0.9557</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0368</v>
+        <v>0.4217</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0536</v>
+        <v>5.4228</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0168</v>
+        <v>2.0502</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0368</v>
+        <v>3.3726</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0108</v>
+        <v>-4.0455</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0108</v>
+        <v>-1.0945</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-2.9509</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1573</v>
+        <v>0.1926</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.7119</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1573</v>
+        <v>-0.5192</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>S. MCKISSIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2805</v>
+        <v>-0.1144</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0268</v>
+        <v>0.0536</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7462</v>
+        <v>-0.168</v>
       </c>
       <c r="G9" t="n">
-        <v>0.716</v>
+        <v>0.0428</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4487</v>
+        <v>0.006</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7327</v>
+        <v>0.0368</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2958</v>
+        <v>0.0536</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3802</v>
+        <v>0.0168</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.0368</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0118</v>
+        <v>-0.0108</v>
       </c>
       <c r="N9" t="n">
-        <v>1.0685</v>
+        <v>-0.0108</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0568</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3772</v>
+        <v>-0.1573</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5885</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2113</v>
+        <v>-0.1573</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3664</v>
+        <v>-0.4499</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4724</v>
+        <v>-1.4986</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8388</v>
+        <v>1.0487</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5364</v>
+        <v>0.716</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3394</v>
+        <v>1.4487</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8031</v>
+        <v>-0.7327</v>
       </c>
       <c r="J10" t="n">
-        <v>5.3093</v>
+        <v>-0.2958</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5829</v>
+        <v>0.3802</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7263</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.7729</v>
+        <v>1.0118</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2435</v>
+        <v>1.0685</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.5294</v>
+        <v>-0.0568</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.639</v>
+        <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2095</v>
+        <v>1.2079</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8022</v>
+        <v>1.1167</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0117</v>
+        <v>0.0912</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1418</v>
+        <v>-1.214</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1418</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.7255</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7536</v>
+        <v>-0.8902</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.746</v>
+        <v>0.1647</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3773</v>
+        <v>-0.7226</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9557</v>
+        <v>-0.0434</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4217</v>
+        <v>-0.6792</v>
       </c>
       <c r="J11" t="n">
-        <v>5.4228</v>
+        <v>0.4031</v>
       </c>
       <c r="K11" t="n">
-        <v>2.0502</v>
+        <v>0.2927</v>
       </c>
       <c r="L11" t="n">
-        <v>3.3726</v>
+        <v>0.1104</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.0455</v>
+        <v>-1.1257</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0945</v>
+        <v>-0.3361</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.9509</v>
+        <v>-0.7896</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q11" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1378</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3497</v>
+        <v>1.0262</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7881</v>
+        <v>-0.1013</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0383</v>
+        <v>-4.4149</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4774</v>
+        <v>-1.8876</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5609</v>
+        <v>-2.5273</v>
       </c>
       <c r="G12" t="n">
         <v>-5.3106</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2095</v>
+        <v>0.4138</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2082</v>
+        <v>0.3815</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0013</v>
+        <v>0.0323</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6778999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6532</v>
+        <v>-5.1477</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5216</v>
+        <v>-3.0498</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1315</v>
+        <v>-2.0979</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4975</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7639</v>
+        <v>-0.2585</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.507</v>
+        <v>-0.0351</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.257</v>
+        <v>-0.2234</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.053900000000001</v>
+        <v>5.053899999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>15.083</v>
+        <v>15.0829</v>
       </c>
       <c r="F14" t="n">
         <v>-10.0291</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6141</v>
+        <v>1.614099999999998</v>
       </c>
       <c r="H14" t="n">
         <v>7.670100000000001</v>
@@ -1549,13 +1549,13 @@
         <v>8.0787</v>
       </c>
       <c r="T14" t="n">
-        <v>9.299899999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2213</v>
+        <v>-1.2211</v>
       </c>
       <c r="V14" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="W14" t="n">
         <v>5.7864</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>J. DOWTIN JR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.873</v>
+        <v>1.9031</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2877</v>
+        <v>2.4757</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4147</v>
+        <v>-0.5726</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4031</v>
+        <v>0.5698</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1655</v>
+        <v>-0.7886</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2375</v>
+        <v>1.3584</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1627</v>
+        <v>3.2652</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6069</v>
+        <v>0.6421</v>
       </c>
       <c r="L15" t="n">
-        <v>1.5557</v>
+        <v>2.6231</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.7596</v>
+        <v>-2.6953</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4414</v>
+        <v>-1.4306</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3182</v>
+        <v>-1.2647</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>3.0154</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0145</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6765</v>
+        <v>0.0868</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.8927</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7886</v>
+        <v>0.2836</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6083</v>
+        <v>0.2836</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5917</v>
+        <v>1.8001</v>
       </c>
       <c r="E16" t="n">
-        <v>3.527</v>
+        <v>3.9339</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9353</v>
+        <v>-2.1338</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4398</v>
+        <v>0.4031</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0755</v>
+        <v>0.1655</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5153</v>
+        <v>0.2375</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9172</v>
+        <v>3.1627</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3983</v>
+        <v>1.6069</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5189</v>
+        <v>1.5557</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4774</v>
+        <v>-2.7596</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4738</v>
+        <v>-1.4414</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0037</v>
+        <v>-1.3182</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6097</v>
+        <v>0.3227</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6176</v>
+        <v>-0.4101</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. DOWTIN JR</t>
+          <t>I. LUNDBERG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2119</v>
+        <v>1.3553</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6501</v>
+        <v>1.7096</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4382</v>
+        <v>-0.3543</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5698</v>
+        <v>1.4754</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7886</v>
+        <v>-0.1608</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3584</v>
+        <v>1.6361</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2652</v>
+        <v>4.2669</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6421</v>
+        <v>0.9446</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6231</v>
+        <v>3.3224</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6953</v>
+        <v>-2.7916</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4306</v>
+        <v>-1.1053</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2647</v>
+        <v>-1.6862</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8556</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R17" t="n">
-        <v>3.0154</v>
+        <v>2.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4971</v>
+        <v>-0.1021</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7389</v>
+        <v>0.244</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7582</v>
+        <v>-0.3462</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2836</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2836</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. LUNDBERG</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3952</v>
+        <v>1.2556</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3557</v>
+        <v>3.0552</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9606</v>
+        <v>-1.7996</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4754</v>
+        <v>0.4398</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1608</v>
+        <v>-0.0755</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6361</v>
+        <v>0.5153</v>
       </c>
       <c r="J18" t="n">
-        <v>4.2669</v>
+        <v>2.9172</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9446</v>
+        <v>1.3983</v>
       </c>
       <c r="L18" t="n">
-        <v>3.3224</v>
+        <v>1.5189</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.7916</v>
+        <v>-2.4774</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1053</v>
+        <v>-1.4738</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6862</v>
+        <v>-1.0037</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7834</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0622</v>
+        <v>-0.344</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1098</v>
+        <v>0.1379</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9524</v>
+        <v>-0.4819</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0543</v>
+        <v>-0.1273</v>
       </c>
       <c r="E19" t="n">
-        <v>0.729</v>
+        <v>0.3752</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7834</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>1.749</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1797</v>
+        <v>-0.2526</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5702</v>
+        <v>0.2164</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7499</v>
+        <v>-0.4689</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. LEAF</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2842</v>
+        <v>-0.2453</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1049</v>
+        <v>-0.0434</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3892</v>
+        <v>-0.2019</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7947</v>
+        <v>-1.6624</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.9386</v>
+        <v>-0.5917</v>
       </c>
       <c r="I20" t="n">
-        <v>0.144</v>
+        <v>-1.0707</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.8757</v>
+        <v>-0.0397</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.0229</v>
+        <v>0.1344</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1472</v>
+        <v>-0.1741</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.919</v>
+        <v>-1.6227</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9157</v>
+        <v>-0.7261</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0033</v>
+        <v>-0.8966</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4173</v>
+        <v>0.1672</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9085</v>
+        <v>-0.0037</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3258</v>
+        <v>0.1709</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>T. LEAF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5091</v>
+        <v>-0.7002</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0746</v>
+        <v>-0.6028</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5837</v>
+        <v>-0.0975</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6624</v>
+        <v>-2.7947</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5917</v>
+        <v>-2.9386</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0707</v>
+        <v>0.144</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0397</v>
+        <v>-1.8757</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1344</v>
+        <v>-2.0229</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1741</v>
+        <v>0.1472</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6227</v>
+        <v>-0.919</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7261</v>
+        <v>-0.9157</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8966</v>
+        <v>-0.0033</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.8334</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1142</v>
+        <v>0.2008</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2109</v>
+        <v>-1.0341</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>J. CLARK III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.267</v>
+        <v>-2.2636</v>
       </c>
       <c r="E22" t="n">
-        <v>0.545</v>
+        <v>-0.4163</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.812</v>
+        <v>-1.8473</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.233</v>
+        <v>0.4371</v>
       </c>
       <c r="H22" t="n">
-        <v>0.377</v>
+        <v>-3.4777</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.61</v>
+        <v>3.9148</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8839</v>
+        <v>1.2739</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6504</v>
+        <v>-2.5404</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7665</v>
+        <v>3.8143</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.1169</v>
+        <v>-0.8368</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2734</v>
+        <v>-0.9373</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.8435</v>
+        <v>0.1005</v>
       </c>
       <c r="P22" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="R22" t="n">
         <v>0.9278</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-2.3195</v>
-      </c>
-      <c r="R22" t="n">
-        <v>3.2473</v>
-      </c>
       <c r="S22" t="n">
-        <v>-0.4257</v>
+        <v>-1.3965</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9085</v>
+        <v>-0.5305</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.3341</v>
+        <v>-0.8661</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4505</v>
+        <v>-2.43</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2389</v>
+        <v>0.1912</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2116</v>
+        <v>-2.6212</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0018</v>
+        <v>-2.233</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1655</v>
+        <v>0.377</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1673</v>
+        <v>-2.61</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6059</v>
+        <v>0.8839</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0672</v>
+        <v>1.6504</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5386</v>
+        <v>-0.7665</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.604</v>
+        <v>-3.1169</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2327</v>
+        <v>-1.2734</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3713</v>
+        <v>-1.8435</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6237</v>
+        <v>3.2473</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6843</v>
+        <v>-0.5887</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5975</v>
+        <v>0.5546</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0868</v>
+        <v>-1.1433</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W23" t="n">
         <v>1.0722</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1444</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. CLARK III</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5604</v>
+        <v>-2.4562</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0061</v>
+        <v>-0.6491</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5543</v>
+        <v>-1.807</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4371</v>
+        <v>0.0018</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.4777</v>
+        <v>-0.1655</v>
       </c>
       <c r="I24" t="n">
-        <v>3.9148</v>
+        <v>0.1673</v>
       </c>
       <c r="J24" t="n">
-        <v>1.2739</v>
+        <v>0.6059</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.5404</v>
+        <v>0.0672</v>
       </c>
       <c r="L24" t="n">
-        <v>3.8143</v>
+        <v>0.5386</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8368</v>
+        <v>-0.604</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9373</v>
+        <v>-0.2327</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1005</v>
+        <v>-0.3713</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.6933</v>
+        <v>-0.6899</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1202</v>
+        <v>-0.0077</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.5731</v>
+        <v>-0.6822</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="25">
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.053700000000001</v>
+        <v>-1.9085</v>
       </c>
       <c r="E25" t="n">
-        <v>10.029</v>
+        <v>10.0292</v>
       </c>
       <c r="F25" t="n">
-        <v>-15.083</v>
+        <v>-11.9377</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.614100000000001</v>
+        <v>-1.6141</v>
       </c>
       <c r="H25" t="n">
         <v>-7.670199999999999</v>
@@ -2395,7 +2395,7 @@
         <v>-8.4475</v>
       </c>
       <c r="P25" t="n">
-        <v>4.638899999999999</v>
+        <v>4.6389</v>
       </c>
       <c r="Q25" t="n">
         <v>-13.9172</v>
@@ -2404,13 +2404,13 @@
         <v>18.5562</v>
       </c>
       <c r="S25" t="n">
-        <v>-8.078600000000002</v>
+        <v>-4.9333</v>
       </c>
       <c r="T25" t="n">
-        <v>1.2212</v>
+        <v>1.2213</v>
       </c>
       <c r="U25" t="n">
-        <v>-9.299799999999999</v>
+        <v>-6.1546</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
